--- a/target/classes/userData.xlsx
+++ b/target/classes/userData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Selenium\OracleSwagLabs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9DE9342-BA20-433C-B67D-AAFC2E17DA2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26CA3B95-9D9C-429C-9554-6B257DD621C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F9F9EB37-E9DF-439C-A1BA-46F4AE58C9EB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>FirstName</t>
   </si>
@@ -49,6 +49,24 @@
   </si>
   <si>
     <t>def</t>
+  </si>
+  <si>
+    <t>mno</t>
+  </si>
+  <si>
+    <t>lkq</t>
+  </si>
+  <si>
+    <t>idvsdv</t>
+  </si>
+  <si>
+    <t>dse</t>
+  </si>
+  <si>
+    <t>mnfdw</t>
+  </si>
+  <si>
+    <t>cjnvejr</t>
   </si>
 </sst>
 </file>
@@ -400,12 +418,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C361B18-02F3-4753-8FB9-6AB560A37393}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -430,6 +448,39 @@
         <v>123</v>
       </c>
     </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>4331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>473</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/target/classes/userData.xlsx
+++ b/target/classes/userData.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Selenium\OracleSwagLabs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26CA3B95-9D9C-429C-9554-6B257DD621C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DE460A-16E2-4C6D-91CD-E09FB381D442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F9F9EB37-E9DF-439C-A1BA-46F4AE58C9EB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F9F9EB37-E9DF-439C-A1BA-46F4AE58C9EB}"/>
   </bookViews>
   <sheets>
     <sheet name="AppData" sheetId="1" r:id="rId1"/>
+    <sheet name="MultiData" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
   <si>
     <t>FirstName</t>
   </si>
@@ -418,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C361B18-02F3-4753-8FB9-6AB560A37393}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -448,36 +449,57 @@
         <v>123</v>
       </c>
     </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EF84871-3918-4C8F-B21E-8651A6A12795}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>4331</v>
+      </c>
+    </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>4331</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
         <v>473</v>
       </c>
     </row>
